--- a/main/ig/StructureDefinition-fr-care-plan-document.xlsx
+++ b/main/ig/StructureDefinition-fr-care-plan-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T10:14:31+00:00</t>
+    <t>2026-07-08T15:46:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-care-plan-document.xlsx
+++ b/main/ig/StructureDefinition-fr-care-plan-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T15:46:54+00:00</t>
+    <t>2026-07-09T09:13:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-care-plan-document.xlsx
+++ b/main/ig/StructureDefinition-fr-care-plan-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:13:13+00:00</t>
+    <t>2026-07-10T12:01:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-care-plan-document.xlsx
+++ b/main/ig/StructureDefinition-fr-care-plan-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T12:01:50+00:00</t>
+    <t>2026-07-10T12:28:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-care-plan-document.xlsx
+++ b/main/ig/StructureDefinition-fr-care-plan-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T12:28:44+00:00</t>
+    <t>2026-07-10T12:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-care-plan-document.xlsx
+++ b/main/ig/StructureDefinition-fr-care-plan-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T12:58:40+00:00</t>
+    <t>2026-07-20T14:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-care-plan-document.xlsx
+++ b/main/ig/StructureDefinition-fr-care-plan-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T14:08:41+00:00</t>
+    <t>2026-07-21T09:08:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-care-plan-document.xlsx
+++ b/main/ig/StructureDefinition-fr-care-plan-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T09:08:11+00:00</t>
+    <t>2026-07-21T09:10:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-care-plan-document.xlsx
+++ b/main/ig/StructureDefinition-fr-care-plan-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T09:10:59+00:00</t>
+    <t>2026-07-22T09:27:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-care-plan-document.xlsx
+++ b/main/ig/StructureDefinition-fr-care-plan-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:27:19+00:00</t>
+    <t>2026-07-28T07:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-care-plan-document.xlsx
+++ b/main/ig/StructureDefinition-fr-care-plan-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T07:28:06+00:00</t>
+    <t>2026-07-30T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-care-plan-document.xlsx
+++ b/main/ig/StructureDefinition-fr-care-plan-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T08:11:50+00:00</t>
+    <t>2026-08-03T07:00:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-care-plan-document.xlsx
+++ b/main/ig/StructureDefinition-fr-care-plan-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T07:00:21+00:00</t>
+    <t>2026-08-04T07:50:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-care-plan-document.xlsx
+++ b/main/ig/StructureDefinition-fr-care-plan-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T07:50:37+00:00</t>
+    <t>2026-08-04T08:17:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-care-plan-document.xlsx
+++ b/main/ig/StructureDefinition-fr-care-plan-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T08:17:33+00:00</t>
+    <t>2026-08-06T12:56:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-care-plan-document.xlsx
+++ b/main/ig/StructureDefinition-fr-care-plan-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T12:56:12+00:00</t>
+    <t>2026-08-07T08:15:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-care-plan-document.xlsx
+++ b/main/ig/StructureDefinition-fr-care-plan-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:15:28+00:00</t>
+    <t>2026-08-07T09:41:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-care-plan-document.xlsx
+++ b/main/ig/StructureDefinition-fr-care-plan-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T09:41:31+00:00</t>
+    <t>2026-08-07T12:53:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-care-plan-document.xlsx
+++ b/main/ig/StructureDefinition-fr-care-plan-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T12:53:43+00:00</t>
+    <t>2026-09-03T14:46:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-care-plan-document.xlsx
+++ b/main/ig/StructureDefinition-fr-care-plan-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T14:46:57+00:00</t>
+    <t>2026-09-04T09:26:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-care-plan-document.xlsx
+++ b/main/ig/StructureDefinition-fr-care-plan-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:26:41+00:00</t>
+    <t>2026-09-04T11:53:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
